--- a/config/config.xlsx
+++ b/config/config.xlsx
@@ -1,34 +1,103 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>input_file</t>
+  </si>
+  <si>
+    <t>input/Consumer Collection Management, Inc. 2.xls</t>
+  </si>
+  <si>
+    <t>sheet_name</t>
+  </si>
+  <si>
+    <t>Sheet1</t>
+  </si>
+  <si>
+    <t>output_file</t>
+  </si>
+  <si>
+    <t>output/valid_remittance.xlsx</t>
+  </si>
+  <si>
+    <t>log_file</t>
+  </si>
+  <si>
+    <t>logs/app.log</t>
+  </si>
+  <si>
+    <t>log_level</t>
+  </si>
+  <si>
+    <t>INFO</t>
+  </si>
+  <si>
+    <t>rule_mode</t>
+  </si>
+  <si>
+    <t>BOTH</t>
+  </si>
+  <si>
+    <t>principal_column</t>
+  </si>
+  <si>
+    <t>Principal</t>
+  </si>
+  <si>
+    <t>interest_column</t>
+  </si>
+  <si>
+    <t>Interest</t>
+  </si>
+  <si>
+    <t>expected_principal_total</t>
+  </si>
+  <si>
+    <t>49090.97</t>
+  </si>
+  <si>
+    <t>expected_interest_total</t>
+  </si>
+  <si>
+    <t>6689.97</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +116,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,144 +418,99 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>input_file</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>input/Consumer Collection Management, Inc. 2.xls</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sheet_name</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Remittance Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>output/valid_remittance.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>log_file</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>logs/app.log</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>log_level</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>rule_mode</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BOTH</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>principal_column</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>interest_column</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Interest</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>expected_principal_total</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>49090.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>expected_interest_total</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>6689.97</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/config/config.xlsx
+++ b/config/config.xlsx
@@ -55,7 +55,7 @@
     <t>rule_mode</t>
   </si>
   <si>
-    <t>BOTH</t>
+    <t>SUM</t>
   </si>
   <si>
     <t>principal_column</t>

--- a/config/config.xlsx
+++ b/config/config.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_F073DF406B8800692F8DB7253744F4ADB0370F4E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8B59B9F-7EB9-45A4-9D3B-C7353D08B476}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="4455" yWindow="2310" windowWidth="9705" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>key</t>
   </si>
@@ -58,41 +59,50 @@
     <t>SUM</t>
   </si>
   <si>
-    <t>principal_column</t>
-  </si>
-  <si>
-    <t>Principal</t>
-  </si>
-  <si>
-    <t>interest_column</t>
-  </si>
-  <si>
-    <t>Interest</t>
-  </si>
-  <si>
     <t>expected_principal_total</t>
   </si>
   <si>
-    <t>49090.97</t>
-  </si>
-  <si>
     <t>expected_interest_total</t>
   </si>
   <si>
-    <t>6689.97</t>
+    <t>master_file</t>
+  </si>
+  <si>
+    <t>input/MasterDatatable_1.xlsx</t>
+  </si>
+  <si>
+    <t>master_sheet</t>
+  </si>
+  <si>
+    <t>master_share_column</t>
+  </si>
+  <si>
+    <t>BWShare</t>
+  </si>
+  <si>
+    <t>client_name</t>
+  </si>
+  <si>
+    <t>principal_col_index</t>
+  </si>
+  <si>
+    <t>interest_col_index</t>
+  </si>
+  <si>
+    <t>IntrestPercentage_Temp2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -115,8 +125,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -132,6 +145,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -418,12 +435,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.42578125" customWidth="1"/>
+    <col min="2" max="2" width="31.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -433,84 +451,130 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1">
+        <v>49090.97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" s="1">
+        <v>6689.97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/config/config.xlsx
+++ b/config/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\B-W\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{057D6011-9AF5-40C9-93A5-41CF4FEA0FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCE39C9-7753-4FB2-BB8C-CD44D8D7DFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,9 +37,6 @@
     <t>sheet_name</t>
   </si>
   <si>
-    <t>Remittance Report</t>
-  </si>
-  <si>
     <t>output_file</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
   </si>
   <si>
     <t>input_folder_temp1</t>
+  </si>
+  <si>
+    <t>Sheet1</t>
   </si>
 </sst>
 </file>
@@ -483,111 +483,111 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
         <v>24</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/config/config.xlsx
+++ b/config/config.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\B-W\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCE39C9-7753-4FB2-BB8C-CD44D8D7DFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253B43D9-D352-42E8-9145-6165AF69CD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>key</t>
   </si>
@@ -37,6 +37,9 @@
     <t>sheet_name</t>
   </si>
   <si>
+    <t>Sheet1</t>
+  </si>
+  <si>
     <t>output_file</t>
   </si>
   <si>
@@ -58,19 +61,7 @@
     <t>rule_mode</t>
   </si>
   <si>
-    <t>BOTH</t>
-  </si>
-  <si>
-    <t>principal_column</t>
-  </si>
-  <si>
-    <t>Principal</t>
-  </si>
-  <si>
-    <t>interest_column</t>
-  </si>
-  <si>
-    <t>Interest</t>
+    <t>SUM</t>
   </si>
   <si>
     <t>expected_principal_total</t>
@@ -88,9 +79,15 @@
     <t>input_file_temp1</t>
   </si>
   <si>
+    <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\B-W\input\jameson and dunagan, p.c..xls</t>
+  </si>
+  <si>
     <t>output_file_temp1</t>
   </si>
   <si>
+    <t>output/temp1_sheet.xlsx</t>
+  </si>
+  <si>
     <t>MasterDatatable</t>
   </si>
   <si>
@@ -100,22 +97,43 @@
     <t>output_template1</t>
   </si>
   <si>
-    <t>output/temp1_sheet.xlsx</t>
-  </si>
-  <si>
     <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\Output\Output.xlsx</t>
   </si>
   <si>
-    <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\B-W\input\jameson and dunagan, p.c..xls</t>
+    <t>input_folder_temp1</t>
   </si>
   <si>
     <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\Input</t>
   </si>
   <si>
-    <t>input_folder_temp1</t>
-  </si>
-  <si>
-    <t>Sheet1</t>
+    <t>master_sheet</t>
+  </si>
+  <si>
+    <t>IntrestPercentage_Temp2</t>
+  </si>
+  <si>
+    <t>master_file</t>
+  </si>
+  <si>
+    <t>input/MasterDatatable_1.xlsx</t>
+  </si>
+  <si>
+    <t>master_share_column</t>
+  </si>
+  <si>
+    <t>BWShare</t>
+  </si>
+  <si>
+    <t>principal_col_index</t>
+  </si>
+  <si>
+    <t>client_name  </t>
+  </si>
+  <si>
+    <t>interest_col_index  </t>
+  </si>
+  <si>
+    <t>principal_col_index  </t>
   </si>
 </sst>
 </file>
@@ -124,7 +142,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -158,7 +176,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -245,6 +263,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -279,6 +298,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -313,20 +333,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -448,21 +464,60 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="100.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -470,7 +525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -478,119 +533,170 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B20" t="s">
         <v>19</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B21" t="s">
         <v>21</v>
       </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    </row>
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="B24" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-    </row>
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B7 A10:B11" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/config/config.xlsx
+++ b/config/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\B-W\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253B43D9-D352-42E8-9145-6165AF69CD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4238B492-291F-423B-8F20-3B1E81E5C7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,21 +91,12 @@
     <t>MasterDatatable</t>
   </si>
   <si>
-    <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\MasterDatatable\MasterDatatable_1.xlsx</t>
-  </si>
-  <si>
     <t>output_template1</t>
   </si>
   <si>
-    <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\Output\Output.xlsx</t>
-  </si>
-  <si>
     <t>input_folder_temp1</t>
   </si>
   <si>
-    <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\Input</t>
-  </si>
-  <si>
     <t>master_sheet</t>
   </si>
   <si>
@@ -134,6 +125,15 @@
   </si>
   <si>
     <t>principal_col_index  </t>
+  </si>
+  <si>
+    <t>..\MasterDatatable\MasterDatatable_1.xlsx</t>
+  </si>
+  <si>
+    <t>..\Output\Output.xlsx</t>
+  </si>
+  <si>
+    <t>..\Input</t>
   </si>
 </sst>
 </file>
@@ -510,14 +510,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="100.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -525,7 +525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -533,7 +533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -541,7 +541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -549,7 +549,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -557,7 +557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -565,7 +565,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -573,23 +573,23 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
         <v>28</v>
       </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -597,7 +597,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -605,54 +605,52 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B14">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -660,7 +658,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -668,31 +666,30 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
       <c r="B22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B23" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>26</v>
-      </c>
       <c r="B24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25"/>
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
